--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.98973078616373</v>
+        <v>12.83583125275161</v>
       </c>
       <c r="D2" t="n">
-        <v>135.3728627626183</v>
+        <v>21.99809019892548</v>
       </c>
       <c r="E2" t="n">
-        <v>21.93248235464232</v>
+        <v>3.564028382629378</v>
       </c>
       <c r="F2" t="n">
-        <v>25.57201259802086</v>
+        <v>4.155452047178388</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.43745217322003</v>
+        <v>6.733585978148255</v>
       </c>
       <c r="D3" t="n">
-        <v>70.84890953427544</v>
+        <v>11.51294779931976</v>
       </c>
       <c r="E3" t="n">
-        <v>21.93248235464232</v>
+        <v>3.564028382629378</v>
       </c>
       <c r="F3" t="n">
-        <v>25.57201259802086</v>
+        <v>4.155452047178388</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.18348983537668</v>
+        <v>4.74231709824871</v>
       </c>
       <c r="D4" t="n">
-        <v>74.7828431450807</v>
+        <v>12.15221201107562</v>
       </c>
       <c r="E4" t="n">
-        <v>21.93248235464232</v>
+        <v>3.564028382629378</v>
       </c>
       <c r="F4" t="n">
-        <v>25.57201259802086</v>
+        <v>4.155452047178388</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.38613161957396</v>
+        <v>3.637746388180768</v>
       </c>
       <c r="D5" t="n">
-        <v>65.2186120644198</v>
+        <v>10.59802446046822</v>
       </c>
       <c r="E5" t="n">
-        <v>21.93248235464232</v>
+        <v>3.564028382629378</v>
       </c>
       <c r="F5" t="n">
-        <v>25.57201259802086</v>
+        <v>4.155452047178388</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.78929774594873</v>
+        <v>11.01576088371667</v>
       </c>
       <c r="D6" t="n">
-        <v>78.97713494568544</v>
+        <v>12.83378442867388</v>
       </c>
       <c r="E6" t="n">
-        <v>21.93248235464232</v>
+        <v>3.564028382629378</v>
       </c>
       <c r="F6" t="n">
-        <v>25.57201259802086</v>
+        <v>4.155452047178388</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
